--- a/output/pdf_financials_xlsx/CFA.H.xlsx
+++ b/output/pdf_financials_xlsx/CFA.H.xlsx
@@ -3090,25 +3090,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.363314</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.363314</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.363314</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.363314</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.363314</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.363314</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.363314</v>
       </c>
     </row>
     <row r="93">
@@ -4847,7 +4847,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -5403,7 +5407,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.363314</v>
       </c>

--- a/output/pdf_financials_xlsx/CFA.H.xlsx
+++ b/output/pdf_financials_xlsx/CFA.H.xlsx
@@ -1393,22 +1393,22 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000249</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000527</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001379</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.390947</v>
       </c>
     </row>
     <row r="35">
@@ -1449,22 +1449,22 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000249</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000527</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001379</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.390947</v>
       </c>
     </row>
     <row r="37">
@@ -1794,13 +1794,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.003692</v>
+        <v>0.002313</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.390947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/CFA.H.xlsx
+++ b/output/pdf_financials_xlsx/CFA.H.xlsx
@@ -5916,7 +5916,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
